--- a/data.mn/public/datasets/mongolbank-sme-loans.xlsx
+++ b/data.mn/public/datasets/mongolbank-sme-loans.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1585,4 +1586,1184 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B116"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>огноо</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>жижиг_дунд_бизнесийн_зээл_тэрбум_төгрөг</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1317.459</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1315.983</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1308.649</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1327.781</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1347.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1403.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1406.192</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1433.783</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1407.776</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2017-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1611.947</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1600.836</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1661.516</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1663.653</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1654.066</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1713.621</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1768.18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2018-05-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1885.629</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2005.941</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2030.288</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2113.599</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2119.732</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2130.116</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2160.161</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2018-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2207.312</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2167.548</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2233.996</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2224.367</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2282.034</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2330.335</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2394.576</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2436.093</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2460.393</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2425.574</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2454.893</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2418.734</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2380.323</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2299.005</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2259.465</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2260.153</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2225.666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2075.276</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2253.587</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2182.91</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2189.519</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2277.482</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1867.521</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1872.594</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1874.172</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2271.978</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2270.976</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2408.619</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2477.298</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2845.145</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3184.581</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3292.061</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3365.548</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3417.86</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3424.947</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3461.021</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3292.871</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3227.91</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3197.895</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3155.012</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3182.713</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>3265.485</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3289.245</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3288.636</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3228.56</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3357.083</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3284.272</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3242.049</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3179.412</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>3174.897</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3151.574</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3097.403</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3067.93</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>3301.821</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3512.514</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>3531.981</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>3538.679</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>3507.108</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3495.103</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>3506.047</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3561.654</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>3418.299</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>3455.263</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>3545.387</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3663.479</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3931.067</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4122.535</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>4021.941</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4018.275</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>4119.411</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>4059.937</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4051.999</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>4069.866</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>4070.343</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>4063.21</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>4103.923</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>4378.439</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>4559.456</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>4912.556</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4849.621</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>4906.007</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>4923.525</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>4959.562</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>4935.89</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>4867.642</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>4786.065</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>4693.794</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>4817.743</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>5262.43</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>5417.017</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>5701.364</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>5631.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/mongolbank-sme-loans.xlsx
+++ b/data.mn/public/datasets/mongolbank-sme-loans.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1581,6 +1581,26 @@
       </c>
       <c r="B116" t="n">
         <v>5631.2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>5613.45</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>5633.922</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2763,6 +2783,26 @@
         <v>5631.2</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>5613.45</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>5633.922</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
